--- a/InputData/endo-learn/PDiBCpDoC/Perc Decline in Battery Cost per Doubling of Cap.xlsx
+++ b/InputData/endo-learn/PDiBCpDoC/Perc Decline in Battery Cost per Doubling of Cap.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\LA\endo-learn\PDiBCpDoC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\endo-learn\PDiBCpDoC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2A607889-2374-4335-88AC-E4107E151D12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2B3602D-03B3-464C-AAF2-F03D8F7520A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Source:</t>
   </si>
@@ -53,9 +53,6 @@
   </si>
   <si>
     <t>Electric Vehicle Outlook 2024</t>
-  </si>
-  <si>
-    <t>Louisiana</t>
   </si>
 </sst>
 </file>
@@ -107,14 +104,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -426,12 +422,6 @@
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1" s="4">
-        <v>45531</v>
-      </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
